--- a/Food Ordering App Test Cases.xlsx
+++ b/Food Ordering App Test Cases.xlsx
@@ -5609,7 +5609,7 @@
         <v>138</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>139</v>
